--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10,7 +10,7 @@
     <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="新增网点（145家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（70家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="减少网点（50家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -478,7 +478,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
+      <c r="C12" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8383</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8458</v>
+        <v>8478</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -6353,339 +6353,339 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+      <c r="A260" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B260" s="4" t="inlineStr">
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C260" s="4" t="n">
+      <c r="C269" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D260" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="4" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="4" t="inlineStr">
+      <c r="D269" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D261" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D262" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="n">
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D263" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="inlineStr">
+      <c r="D272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="n">
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D264" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="4" t="inlineStr">
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="n">
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D265" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C266" s="4" t="n">
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="n">
+      <c r="D275" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D267" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D268" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D270" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E273" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E274" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D275" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E275" s="4" t="n">
-        <v>-1</v>
+      <c r="E275" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14795,7 +14795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15769,27 +15769,27 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>意特汽车商业（上海）有限公司</t>
+          <t>北京中关村大融城</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>恒通东路69号101单元 龙盛福新汇 上海 上海</t>
+          <t>北京市海淀区中关村大街路中关村ART PARK大融城东区LG2层B2小中庭</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -15801,27 +15801,27 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>昆明乐骏汽车销售服务有限公司</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>滇池度假区滇池路1103号平安大厦B座1层 平安大厦 昆明市 滇池度假区</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15833,27 +15833,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>北京骏东汽车销售服务有限公司</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>金宝街 金宝大厦一层 北京 东城区</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -15865,59 +15865,59 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>成都骏意汽车销售服务有限公司</t>
+          <t>佛山顺德特斯拉中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>佛山市</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>成都市高新区火车南站西路 法拉利 成都市 中国</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段新协力汽车城</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 13 期；本期存在高相似店名「佛山顺德北滘特斯拉中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>安徽鸿粤鸿超汽车销售服务有限公司</t>
+          <t>杭州万象城城市展厅B1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>花亭湖路与齐云山路交叉口 安徽鸿粤鸿超汽车销售服务有限公司 合肥 蜀山区</t>
+          <t>浙江省杭州市上城区富春路701号 B1</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -15929,27 +15929,27 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>青岛恒骏汽车销售服务有限公司</t>
+          <t>蔚来空间 | 昆明七彩云南第壹Mall</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>昆明市</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>青岛市市南区东海西路1号1号楼丙户 青岛市 市南区</t>
+          <t>云南省昆明市呈贡区彩云南路七彩云南第壹Mall 1号门</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -15961,27 +15961,27 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>广东骏佳汽车服务有限公司</t>
+          <t>蔚来空间 | 成都城西优品道广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>天河区珠江新城清风街1-48号 新世界广场首层 Guangzhou</t>
+          <t>四川省成都市青羊区青羊大道99号</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -15993,27 +15993,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>骏佳行汽车服务（深圳）有限公司</t>
+          <t>蔚来空间 | 信阳西亚城</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>中心路1号 深圳湾壹号北区2栋 Shenzhen Nanshan District</t>
+          <t>河南省信阳市平桥区行政路西亚城LG-25店铺</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -16025,27 +16025,27 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>南京瑞骏汽车销售服务有限公司</t>
+          <t>蔚来空间 | 杭州滨江银泰</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>长江路100号 长江会 南京 玄武</t>
+          <t>浙江省杭州市滨江区西兴街道启智街515号滨江银泰B-147</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -16057,59 +16057,59 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>苏州意骏汽车销售服务有限公司</t>
+          <t>蔚来中心 | 湖州浙北大厦</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>湖州市</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区思安街99号协鑫广场西侧1F Suzhou</t>
+          <t>浙江省湖州市吴兴区南街697号浙北大厦购物中心A侧门1号铺位</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 11 期</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>郑州悦骏汽车销售服务有限公司</t>
+          <t>蔚来空间 | 大连华南万象汇</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>大连市</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>如意西路 中国平煤神马集团 郑州 郑东新区</t>
+          <t>辽宁省大连市甘井子区山东路350号、352号 华南万象汇 LG216商铺</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -16121,27 +16121,27 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>宁波骏意汽车服务有限公司</t>
+          <t>蔚来空间 | 重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>中官新路 A号楼 Ningbo Jiangbei District</t>
+          <t>重庆市渝北区礼慈路龙湖礼嘉天街A馆1F-37</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -16153,27 +16153,27 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>杭州骏意汽车销售服务有限公司</t>
+          <t>华为智能生活馆•包头昆区吾悦广场</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>包头市</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市南山路 杭州 上城区</t>
+          <t>内蒙古自治区包头市昆都仑区林荫路与稀土大街交汇处西南角吾悦广场1层华为智能生活</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -16185,27 +16185,27 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>温州骏意汽车服务有限公司</t>
+          <t>华为授权体验店（维多利喜悦汇）</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>呼和浩特市</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>温州经济技术开发区滨海园区 3号4S店东侧 温州 中国</t>
+          <t>内蒙古自治区呼和浩特市新城区北二环路与北二环快速路入口交叉口东南200米维多利喜悦汇一层</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -16217,27 +16217,27 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>武汉骏东汽车销售服务有限公司</t>
+          <t>华为智能生活馆•潍坊谷德广场</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>潍坊市</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>解放大道634号K11步行街 108-109 武汉 中国</t>
+          <t>山东省潍坊市高新区福寿东街4369号谷德广场1楼</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -16249,27 +16249,27 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>长沙市骏马汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>濮阳市</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>潇湘北路 圆泰长沙印 103-1 号 长沙市 中国</t>
+          <t>河南省濮阳市濮阳县龙都瑞璞汽车小镇7幢1号</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -16281,91 +16281,91 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>福建骏佳行汽车销售服务有限公司</t>
+          <t>华为授权体验店（嵩南印象城）</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>厦门市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>环岛东路1821号 中航紫金广场商业街 厦门市 思明区</t>
+          <t>河南省郑州市嵩山南路与柳江路交叉口嵩南印象城L1-05</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（印象城）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>沈阳鸿粤鸿福汽车销售服务有限公司</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>沈阳市</t>
+          <t>台州市</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>浑南区全运路 Shenyang China</t>
+          <t>浙江省台州市椒江经开万达1F1063、1065、1066号铺</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 13 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>重庆骏东汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•杭州国际汽车城</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>重庆两江新区新南路 龙湖晶郦馆A栋-1F-03b Chongqing New South St</t>
+          <t>浙江省杭州市拱墅区花园岗街205号</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -16377,27 +16377,27 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为智能生活馆•绍兴诸暨万风新天地</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>绍兴市</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>浙江省绍兴市诸暨市暨阳街道苎萝东路555号雄风新天地</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -16409,670 +16409,30 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>北京中关村大融城</t>
+          <t>【测试】HIMA授权交付中心</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>阿里地区</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>北京市海淀区中关村大街路中关村ART PARK大融城东区LG2层B2小中庭</t>
+          <t>官方将安排优质的门店尽快与您联系</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>成都市</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>成都天府公园111体验店</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>成都市</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>佛山顺德特斯拉中心</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>佛山市</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段新协力汽车城</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期；本期存在高相似店名「佛山顺德北滘特斯拉中心」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>杭州万象城城市展厅B1</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>浙江省杭州市上城区富春路701号 B1</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 昆明七彩云南第壹Mall</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>昆明市</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>云南省昆明市呈贡区彩云南路七彩云南第壹Mall 1号门</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 成都城西优品道广场</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>成都市</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>四川省成都市青羊区青羊大道99号</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 信阳西亚城</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>信阳市</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>河南省信阳市平桥区行政路西亚城LG-25店铺</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 杭州滨江银泰</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>浙江省杭州市滨江区西兴街道启智街515号滨江银泰B-147</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>蔚来中心 | 湖州浙北大厦</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>湖州市</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>浙江省湖州市吴兴区南街697号浙北大厦购物中心A侧门1号铺位</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 11 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 大连华南万象汇</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>大连市</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>辽宁省大连市甘井子区山东路350号、352号 华南万象汇 LG216商铺</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 重庆龙湖礼嘉天街</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>重庆市渝北区礼慈路龙湖礼嘉天街A馆1F-37</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•包头昆区吾悦广场</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>包头市</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古自治区包头市昆都仑区林荫路与稀土大街交汇处西南角吾悦广场1层华为智能生活</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>华为授权体验店（维多利喜悦汇）</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>呼和浩特市</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古自治区呼和浩特市新城区北二环路与北二环快速路入口交叉口东南200米维多利喜悦汇一层</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•潍坊谷德广场</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>潍坊市</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>山东省潍坊市高新区福寿东街4369号谷德广场1楼</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•濮阳瑞璞汽车小镇</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>濮阳市</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>河南省濮阳市濮阳县龙都瑞璞汽车小镇7幢1号</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>华为授权体验店（嵩南印象城）</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>郑州市</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>河南省郑州市嵩山南路与柳江路交叉口嵩南印象城L1-05</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（印象城）」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>华为授权体验店（万达广场）</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>台州市</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>浙江省台州市椒江经开万达1F1063、1065、1066号铺</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•杭州国际汽车城</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>浙江省杭州市拱墅区花园岗街205号</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•绍兴诸暨万风新天地</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>绍兴市</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>浙江省绍兴市诸暨市暨阳街道苎萝东路555号雄风新天地</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 13 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>【测试】HIMA授权交付中心</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>阿里地区</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>官方将安排优质的门店尽快与您联系</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>连续在档 1 期</t>
         </is>
@@ -17145,12 +16505,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -17160,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -17172,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -17192,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -17204,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -17224,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -17268,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -17288,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -17300,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -17320,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -17332,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -17352,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -17364,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -17384,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -17396,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -17416,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -17428,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -17448,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -17460,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -17480,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -17492,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -17512,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -17524,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -17544,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -17588,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -17608,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -17620,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17640,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -17684,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17704,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -17743,22 +17103,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17775,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17812,17 +17172,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17839,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17903,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17972,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -18004,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -18068,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -18088,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -18100,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -18120,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -18159,22 +17519,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -18184,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -18216,7 +17576,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -18228,17 +17588,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -18248,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（145家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（50家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（145家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（50家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,29 +16552,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,29 +16584,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,29 +16712,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17135,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17524,17 +17524,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（145家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（50家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（145家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（50家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（35条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,29 +16552,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,14 +16712,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -16729,12 +16729,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,29 +16808,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,29 +17064,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -17108,17 +17108,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17204,17 +17204,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -17556,17 +17556,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,29 +16648,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,29 +16808,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,29 +17064,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -17108,17 +17108,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17135,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,29 +16648,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,29 +16744,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16793,12 +16793,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,29 +16840,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17236,17 +17236,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17588,17 +17588,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,29 +16584,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16633,12 +16633,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16697,12 +16697,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,29 +16744,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16793,12 +16793,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,29 +16840,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17300,17 +17300,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17359,22 +17359,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17556,17 +17556,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,14 +16584,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -16601,12 +16601,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16697,12 +16697,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,29 +16712,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,29 +16744,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,7 +17295,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -17305,12 +17305,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17359,7 +17359,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -17369,12 +17369,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -17583,22 +17583,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
